--- a/株売買アドバイス/202604/株式運用ログ_202604.xlsx
+++ b/株売買アドバイス/202604/株式運用ログ_202604.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>宇宙・防衛テーマ継続。中東紛争で注目度維持</t>
         </is>
       </c>
       <c r="J15" s="19" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>インバウンド底堅いが円高リスクに注意</t>
         </is>
       </c>
       <c r="J16" s="19" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>半導体需要回復で含み損縮小傾向</t>
         </is>
       </c>
       <c r="J17" s="19" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>ポジション微小。動向監視</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="K18" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>エンタメ・半導体部門安定。含み益維持</t>
         </is>
       </c>
       <c r="J19" s="19" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="K19" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>AI向けテスタ需要過去最高。決算好調で注目</t>
         </is>
       </c>
       <c r="J20" s="19" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>保有継続</t>
+          <t>様子見</t>
         </is>
       </c>
       <c r="F21" s="21" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>中国需要回復待ち。原油高は製造業に逆風</t>
         </is>
       </c>
       <c r="J21" s="19" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K21" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>保有継続</t>
+          <t>様子見</t>
         </is>
       </c>
       <c r="F22" s="21" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>停戦協議進展で防衛プレミアム剥落リスク</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>半導体装置需要回復。含み損ほぼ解消</t>
         </is>
       </c>
       <c r="J23" s="19" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>保有継続</t>
+          <t>様子見</t>
         </is>
       </c>
       <c r="F24" s="21" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>Switch2生産削減で下落継続。反転確認まで慎重</t>
         </is>
       </c>
       <c r="J24" s="19" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>Switch2実売データ・次回決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>AI投資拡大で中長期は期待維持</t>
         </is>
       </c>
       <c r="J25" s="19" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
-          <t>web検索による週次分析（4/14）</t>
+          <t>国内消費強く最高パフォーマンス。利確タイミング検討</t>
         </is>
       </c>
       <c r="J26" s="19" t="inlineStr">
@@ -1827,29 +1827,633 @@
       </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
-          <t>中東情勢・イラン停戦協議が最大変数</t>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="10">
-        <f>SUM(H15:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>290A</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Synspective</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>1363</v>
+      </c>
+      <c r="H27" s="23">
+        <f>F27*G27</f>
+        <v/>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>宇宙・防衛テーマ継続</t>
+        </is>
+      </c>
+      <c r="J27" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議・決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>4661</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>オリエンタルランド</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <v>2635</v>
+      </c>
+      <c r="H28" s="23">
+        <f>F28*G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>インバウンド底堅い</t>
+        </is>
+      </c>
+      <c r="J28" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議・決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>6146</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>ディスコ</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>72894</v>
+      </c>
+      <c r="H29" s="23">
+        <f>F29*G29</f>
+        <v/>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>含み益転換！半導体需要回復</t>
+        </is>
+      </c>
+      <c r="J29" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>6460</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>セガサミーHD</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>2551</v>
+      </c>
+      <c r="H30" s="23">
+        <f>F30*G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>ポジション微小</t>
+        </is>
+      </c>
+      <c r="J30" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>動向監視</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>6758</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>ソニーグループ</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>3395</v>
+      </c>
+      <c r="H31" s="23">
+        <f>F31*G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>AI関連株調整でゲーム・IP株に見直し買い流入</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>6857</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>アドバンテスト</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>27921</v>
+      </c>
+      <c r="H32" s="23">
+        <f>F32*G32</f>
+        <v/>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>AI需要継続。+5.53%で好調維持</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>ファナック</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>6230</v>
+      </c>
+      <c r="H33" s="23">
+        <f>F33*G33</f>
+        <v/>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>中国需要回復待ち</t>
+        </is>
+      </c>
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>中国景況感指標確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>三菱重工業</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>4371</v>
+      </c>
+      <c r="H34" s="23">
+        <f>F34*G34</f>
+        <v/>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>停戦で防衛プレミアム剥落。-14.36%まで悪化</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
+          <t>4,300円割れなら損切り検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>7735</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>SCREENホールディングス</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>21175</v>
+      </c>
+      <c r="H35" s="23">
+        <f>F35*G35</f>
+        <v/>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>半導体装置、含み損再拡大。様子見</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K35" s="20" t="inlineStr">
+        <is>
+          <t>半導体装置受注動向確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>8619</v>
+      </c>
+      <c r="H36" s="23">
+        <f>F36*G36</f>
+        <v/>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>含み益転換！ゲーム株見直し買い</t>
+        </is>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>Switch2実売継続確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>東京エレクトロン</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>44092</v>
+      </c>
+      <c r="H37" s="23">
+        <f>F37*G37</f>
+        <v/>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>微小含み益。AI投資継続期待</t>
+        </is>
+      </c>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>9983</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>ファーストリテイリング</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>74463</v>
+      </c>
+      <c r="H38" s="23">
+        <f>F38*G38</f>
+        <v/>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>取得比+10.95%。利確タイミング意識</t>
+        </is>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>次回決算前に利確検討</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1870,7 +2474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2645,40 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/19</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>717202</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="24">
+        <f>IFERROR(D7/(C7+D7),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-291</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(F7/(C7-F7),0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>日経平均4/16に史上最高値59,518円更新。週間+1,552円。取得原価まで291円に迫る</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2052,7 +2690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2460,7 +3098,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>6758 ソニーグループ</t>
+          <t>6460 セガサミーHD</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
@@ -2476,7 +3114,7 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>エンタメ・半導体部門安定。含み益維持</t>
+          <t>ポジション微小。動向監視</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -2493,7 +3131,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>6857 アドバンテスト</t>
+          <t>6758 ソニーグループ</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
@@ -2504,12 +3142,12 @@
       <c r="D18" s="19" t="inlineStr"/>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>AI向けテスタ需要過去最高。決算好調で注目</t>
+          <t>エンタメ・半導体部門安定。含み益維持</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -2526,23 +3164,23 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>6954 ファナック</t>
+          <t>6857 アドバンテスト</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>様子見</t>
+          <t>保有継続</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>中国需要回復待ち。原油高は製造業に逆風</t>
+          <t>AI向けテスタ需要過去最高。決算好調で注目</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -2559,7 +3197,7 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>7011 三菱重工業</t>
+          <t>6954 ファナック</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
@@ -2575,7 +3213,7 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>停戦協議進展で防衛プレミアム剥落リスク</t>
+          <t>中国需要回復待ち。原油高は製造業に逆風</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -2592,12 +3230,12 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>7735 SCREENホールディングス</t>
+          <t>7011 三菱重工業</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>保有継続</t>
+          <t>様子見</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr"/>
@@ -2608,7 +3246,7 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>半導体装置需要回復。含み損ほぼ解消</t>
+          <t>停戦協議進展で防衛プレミアム剥落リスク</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -2625,23 +3263,23 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>7974 任天堂</t>
+          <t>7735 SCREENホールディングス</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>様子見</t>
+          <t>保有継続</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr"/>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Switch2生産削減報道で下落継続。反転確認まで慎重</t>
+          <t>半導体装置需要回復。含み損ほぼ解消</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -2658,28 +3296,28 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>8035 東京エレクトロン</t>
+          <t>7974 任天堂</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>保有継続</t>
+          <t>様子見</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>×</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>AI投資拡大で中長期は期待維持</t>
+          <t>Switch2生産削減で下落継続。反転確認まで慎重</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
+          <t>Switch2実売データ・次回決算ガイダンスを確認</t>
         </is>
       </c>
     </row>
@@ -2691,7 +3329,7 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>9983 ファーストリテイリング</t>
+          <t>8035 東京エレクトロン</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
@@ -2707,12 +3345,441 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
+          <t>AI投資拡大で中長期は期待維持</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>来週の停戦協議結果・決算ガイダンスを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>第1週(4月)</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>9983 ファーストリテイリング</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr"/>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
           <t>国内消費強く最高パフォーマンス。利確タイミング検討</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>来週の停戦協議結果・決算ガイダンスを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>290A Synspective</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr"/>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>宇宙・防衛テーマ継続</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議・決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>4661 オリエンタルランド</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr"/>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>インバウンド底堅い</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議・決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>6146 ディスコ</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr"/>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>含み益転換！半導体需要回復</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>6460 セガサミーHD</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr"/>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>ポジション微小</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>動向監視</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>6758 ソニーグループ</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr"/>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>AI関連株調整でゲーム・IP株に見直し買い流入</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>6857 アドバンテスト</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr"/>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>AI需要継続。+5.53%で好調維持</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>6954 ファナック</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr"/>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>中国需要回復待ち</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>中国景況感指標確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>7011 三菱重工業</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr"/>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>停戦で防衛プレミアム剥落。-14.36%まで悪化</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>4,300円割れなら損切り検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>7735 SCREENホールディングス</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr"/>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>半導体装置、含み損再拡大。様子見</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>半導体装置受注動向確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>7974 任天堂</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr"/>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>含み益転換！ゲーム株見直し買い</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>Switch2実売継続確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>8035 東京エレクトロン</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr"/>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>微小含み益。AI投資継続期待</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>第2週(4月)</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>9983 ファーストリテイリング</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr"/>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>取得比+10.95%。利確タイミング意識</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>次回決算前に利確検討</t>
         </is>
       </c>
     </row>
@@ -2823,7 +3890,7 @@
         <v>124500</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>136700</v>
@@ -2863,7 +3930,7 @@
         <v>49999</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>2608</v>
+        <v>2635</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>48712</v>
@@ -2903,7 +3970,7 @@
         <v>30000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>71062</v>
+        <v>72894</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>28803</v>
@@ -2983,7 +4050,7 @@
         <v>163000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3302</v>
+        <v>3395</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>163550</v>
@@ -3023,7 +4090,7 @@
         <v>49999</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>26808</v>
+        <v>27921</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>45402</v>
@@ -3063,7 +4130,7 @@
         <v>49999</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>6269</v>
+        <v>6230</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>42933</v>
@@ -3103,7 +4170,7 @@
         <v>99999</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4774</v>
+        <v>4371</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>94984</v>
@@ -3143,7 +4210,7 @@
         <v>29999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>22435</v>
+        <v>21175</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>26656</v>
@@ -3183,7 +4250,7 @@
         <v>99999</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>8318</v>
+        <v>8619</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>114222</v>
@@ -3223,7 +4290,7 @@
         <v>10000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>43632</v>
+        <v>44092</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>8984</v>
@@ -3263,7 +4330,7 @@
         <v>10000</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>75027</v>
+        <v>74463</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>9504</v>

--- a/株売買アドバイス/202604/株式運用ログ_202604.xlsx
+++ b/株売買アドバイス/202604/株式運用ログ_202604.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2450,6 +2450,578 @@
         </is>
       </c>
       <c r="K38" s="20" t="inlineStr">
+        <is>
+          <t>次回決算前に利確検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>290A</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Synspective</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>1330</v>
+      </c>
+      <c r="H39" s="23">
+        <f>F39*G39</f>
+        <v/>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>宇宙・防衛テーマ継続</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議動向確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>4661</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>オリエンタルランド</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>2401</v>
+      </c>
+      <c r="H40" s="23">
+        <f>F40*G40</f>
+        <v/>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>4/28決算前の警戒売りで-14.16%まで悪化</t>
+        </is>
+      </c>
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="K40" s="20" t="inlineStr">
+        <is>
+          <t>4/28決算のガイダンス確認後に判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>6146</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>ディスコ</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>71693</v>
+      </c>
+      <c r="H41" s="23">
+        <f>F41*G41</f>
+        <v/>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>半導体需要回復期待は継続</t>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>6758</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>ソニーグループ</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>3208</v>
+      </c>
+      <c r="H42" s="23">
+        <f>F42*G42</f>
+        <v/>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>メモリ高騰でゲーム事業採算悪化懸念。9,350円急落</t>
+        </is>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="K42" s="20" t="inlineStr">
+        <is>
+          <t>決算でメモリコスト影響の開示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>6857</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>アドバンテスト</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G43" s="22" t="n">
+        <v>29492</v>
+      </c>
+      <c r="H43" s="23">
+        <f>F43*G43</f>
+        <v/>
+      </c>
+      <c r="I43" s="20" t="inlineStr">
+        <is>
+          <t>AI需要継続で+11.48%。好調維持</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K43" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>ファナック</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="G44" s="22" t="n">
+        <v>6259</v>
+      </c>
+      <c r="H44" s="23">
+        <f>F44*G44</f>
+        <v/>
+      </c>
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t>中国需要回復待ち</t>
+        </is>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K44" s="20" t="inlineStr">
+        <is>
+          <t>中国景況感指標確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>三菱重工業</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="G45" s="22" t="n">
+        <v>4738</v>
+      </c>
+      <c r="H45" s="23">
+        <f>F45*G45</f>
+        <v/>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>イラン停戦暗礁で防衛株V字回復+7,192円</t>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議の行方を継続監視</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>7735</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>SCREENホールディングス</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>21378</v>
+      </c>
+      <c r="H46" s="23">
+        <f>F46*G46</f>
+        <v/>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>半導体装置、小幅回復</t>
+        </is>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
+        <is>
+          <t>受注動向確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="G47" s="22" t="n">
+        <v>7955</v>
+      </c>
+      <c r="H47" s="23">
+        <f>F47*G47</f>
+        <v/>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>メモリコスト問題で再び-6.67%。含み損再拡大</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>決算でSwitch2採算性の開示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>東京エレクトロン</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="G48" s="22" t="n">
+        <v>45934</v>
+      </c>
+      <c r="H48" s="23">
+        <f>F48*G48</f>
+        <v/>
+      </c>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t>AI投資継続で微小含み益継続</t>
+        </is>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K48" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>9983</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>ファーストリテイリング</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="G49" s="22" t="n">
+        <v>70483</v>
+      </c>
+      <c r="H49" s="23">
+        <f>F49*G49</f>
+        <v/>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>取得比+5.02%。利確タイミング引き続き意識</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K49" s="20" t="inlineStr">
         <is>
           <t>次回決算前に利確検討</t>
         </is>
@@ -2474,7 +3046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2679,6 +3251,40 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>2026/4/26</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>702546</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="24">
+        <f>IFERROR(D8/(C8+D8),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-14946</v>
+      </c>
+      <c r="G8" s="24">
+        <f>IFERROR(F8/(C8-F8),0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>日経4/16最高値後に調整。ソニー・任天堂メモリコスト懸念で急落。三菱重工は停戦協議暗礁で+7,192円回復</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2690,7 +3296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3778,6 +4384,369 @@
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>次回決算前に利確検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>290A Synspective</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr"/>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>宇宙・防衛テーマ継続</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議動向確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>4661 オリエンタルランド</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr"/>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>4/28決算前の警戒売りで-14.16%まで悪化</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>4/28決算のガイダンス確認後に判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>6146 ディスコ</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr"/>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>半導体需要回復期待は継続</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>6758 ソニーグループ</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>メモリ高騰でゲーム事業採算悪化懸念。9,350円急落</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>決算でメモリコスト影響の開示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>6857 アドバンテスト</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr"/>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>AI需要継続で+11.48%。好調維持</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>6954 ファナック</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr"/>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>中国需要回復待ち</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>中国景況感指標確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>7011 三菱重工業</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr"/>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>イラン停戦暗礁で防衛株V字回復+7,192円</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>停戦協議の行方を継続監視</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>7735 SCREENホールディングス</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr"/>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>半導体装置、小幅回復</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>受注動向確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>7974 任天堂</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>様子見</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr"/>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>メモリコスト問題で再び-6.67%。含み損再拡大</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>決算でSwitch2採算性の開示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>8035 東京エレクトロン</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr"/>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>AI投資継続で微小含み益継続</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>決算ガイダンス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>9983 ファーストリテイリング</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>保有継続</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr"/>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>取得比+5.02%。利確タイミング引き続き意識</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>次回決算前に利確検討</t>
         </is>
@@ -3890,7 +4859,7 @@
         <v>124500</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1363</v>
+        <v>1330</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>136700</v>
@@ -3930,7 +4899,7 @@
         <v>49999</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>2635</v>
+        <v>2401</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>48712</v>
@@ -3970,7 +4939,7 @@
         <v>30000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>72894</v>
+        <v>71693</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>28803</v>
@@ -4010,7 +4979,7 @@
         <v>1914</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2551</v>
+        <v>3208</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1915</v>
@@ -4050,7 +5019,7 @@
         <v>163000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3395</v>
+        <v>29492</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>163550</v>
@@ -4090,7 +5059,7 @@
         <v>49999</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>27921</v>
+        <v>6259</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>45402</v>
@@ -4130,7 +5099,7 @@
         <v>49999</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>6230</v>
+        <v>4738</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>42933</v>
@@ -4170,7 +5139,7 @@
         <v>99999</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4371</v>
+        <v>21378</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>94984</v>
@@ -4210,7 +5179,7 @@
         <v>29999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>21175</v>
+        <v>7955</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>26656</v>
@@ -4250,7 +5219,7 @@
         <v>99999</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>8619</v>
+        <v>45934</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>114222</v>
@@ -4290,7 +5259,7 @@
         <v>10000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>44092</v>
+        <v>70483</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>8984</v>

--- a/株売買アドバイス/202604/株式運用ログ_202604.xlsx
+++ b/株売買アドバイス/202604/株式運用ログ_202604.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,6 +173,10 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3296,7 +3300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4749,6 +4753,151 @@
       <c r="G48" s="20" t="inlineStr">
         <is>
           <t>次回決算前に利確検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>【新規購入検討候補】</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="n"/>
+      <c r="C49" s="27" t="n"/>
+      <c r="D49" s="27" t="n"/>
+      <c r="E49" s="27" t="n"/>
+      <c r="F49" s="27" t="n"/>
+      <c r="G49" s="27" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>2802 味の素</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>新規検討</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>食品・化学素材 / ¥4,758</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr"/>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>AI向けABF絶縁フィルムで世界シェア約95%。半導体パッケージ需要の直接受益者。食品事業との複合で景気後退耐性も高い</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>AI設備投資縮小リスク・食品事業の原材料コスト上昇</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>6976 太陽誘電</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>新規検討</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>電子部品 / ¥6,508</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr"/>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>AIサーバー向けMLCC需要急増。3Q営業利益前年比+96.6%。車載・AI向け積層セラコンで成長継続見込み</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>中国生産依存・地政学リスク。半導体市況の急変動に注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>8306 三菱UFJフィナンシャル</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>新規検討</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>金融 / ¥2,760</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr"/>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>日銀利上げ継続で利ザヤ拡大。配当74円・利回り約2.68%。現ポートフォリオに金融セクター未保有で分散効果大</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>景気後退時の貸倒リスク・円高転換で海外資産の評価額下落</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>第3週(4月)</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>8750 第一生命HD</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>新規検討</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>保険 / ¥1,411</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr"/>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>金利上昇恩恵・海外保険事業拡大。増配継続見通し。保険セクターは現ポートフォリオ未保有</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>円高・株安で資産運用収益悪化リスク。海外損保の自然災害リスク</t>
         </is>
       </c>
     </row>
@@ -4979,7 +5128,7 @@
         <v>1914</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>3208</v>
+        <v>2551</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1915</v>
@@ -5019,7 +5168,7 @@
         <v>163000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>29492</v>
+        <v>3208</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>163550</v>
@@ -5059,7 +5208,7 @@
         <v>49999</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>6259</v>
+        <v>29492</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>45402</v>
@@ -5099,7 +5248,7 @@
         <v>49999</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4738</v>
+        <v>6259</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>42933</v>
@@ -5139,7 +5288,7 @@
         <v>99999</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>21378</v>
+        <v>4738</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>94984</v>
@@ -5179,7 +5328,7 @@
         <v>29999</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>7955</v>
+        <v>21378</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>26656</v>
@@ -5219,7 +5368,7 @@
         <v>99999</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>45934</v>
+        <v>7955</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>114222</v>
@@ -5259,7 +5408,7 @@
         <v>10000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>70483</v>
+        <v>45934</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>8984</v>
@@ -5299,7 +5448,7 @@
         <v>10000</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>74463</v>
+        <v>70483</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>9504</v>
